--- a/dataset_t6_grouped/results2/G5/G5_T12594_W0065F0002T0006Z000C1N22_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T12594_W0065F0002T0006Z000C1N22_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>10.66013705898951</v>
+        <v>1.732272272085795</v>
       </c>
       <c r="D2" t="n">
-        <v>10.29956196415481</v>
+        <v>1.673678819175157</v>
       </c>
       <c r="E2" t="n">
-        <v>10.73532228841562</v>
+        <v>1.744489871867538</v>
       </c>
       <c r="F2" t="n">
-        <v>10.29871856001947</v>
+        <v>1.673541766003165</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>16.453766962823</v>
+        <v>2.673737131458738</v>
       </c>
       <c r="D3" t="n">
-        <v>16.88773048852106</v>
+        <v>2.744256204384673</v>
       </c>
       <c r="E3" t="n">
-        <v>10.73532228841562</v>
+        <v>1.744489871867538</v>
       </c>
       <c r="F3" t="n">
-        <v>10.29871856001947</v>
+        <v>1.673541766003165</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>31.73350142255282</v>
+        <v>5.156693981164833</v>
       </c>
       <c r="D4" t="n">
-        <v>31.07527368502928</v>
+        <v>5.049731973817259</v>
       </c>
       <c r="E4" t="n">
-        <v>10.73532228841562</v>
+        <v>1.744489871867538</v>
       </c>
       <c r="F4" t="n">
-        <v>10.29871856001947</v>
+        <v>1.673541766003165</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>20.70788003993398</v>
+        <v>3.365030506489272</v>
       </c>
       <c r="D5" t="n">
-        <v>20.36626052600649</v>
+        <v>3.309517335476055</v>
       </c>
       <c r="E5" t="n">
-        <v>10.73532228841562</v>
+        <v>1.744489871867538</v>
       </c>
       <c r="F5" t="n">
-        <v>10.29871856001947</v>
+        <v>1.673541766003165</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>44.66665433510401</v>
+        <v>7.258331329454402</v>
       </c>
       <c r="D6" t="n">
-        <v>45.08075229672249</v>
+        <v>7.325622248217404</v>
       </c>
       <c r="E6" t="n">
-        <v>10.73532228841562</v>
+        <v>1.744489871867538</v>
       </c>
       <c r="F6" t="n">
-        <v>10.29871856001947</v>
+        <v>1.673541766003165</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>28.32690604166494</v>
+        <v>4.603122231770553</v>
       </c>
       <c r="D7" t="n">
-        <v>27.28688386234441</v>
+        <v>4.434118627630967</v>
       </c>
       <c r="E7" t="n">
-        <v>10.73532228841562</v>
+        <v>1.744489871867538</v>
       </c>
       <c r="F7" t="n">
-        <v>10.29871856001947</v>
+        <v>1.673541766003165</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>13.34952699552834</v>
+        <v>2.169298136773355</v>
       </c>
       <c r="D8" t="n">
-        <v>12.25728274576691</v>
+        <v>1.991808446187123</v>
       </c>
       <c r="E8" t="n">
-        <v>10.73532228841562</v>
+        <v>1.744489871867538</v>
       </c>
       <c r="F8" t="n">
-        <v>10.29871856001947</v>
+        <v>1.673541766003165</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>40.9940655534939</v>
+        <v>6.66153565244276</v>
       </c>
       <c r="D9" t="n">
-        <v>27.2232842584659</v>
+        <v>4.423783692000709</v>
       </c>
       <c r="E9" t="n">
-        <v>10.73532228841562</v>
+        <v>1.744489871867538</v>
       </c>
       <c r="F9" t="n">
-        <v>10.29871856001947</v>
+        <v>1.673541766003165</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>24.70539529220673</v>
+        <v>4.014626734983594</v>
       </c>
       <c r="D10" t="n">
-        <v>23.98971228646845</v>
+        <v>3.898328246551124</v>
       </c>
       <c r="E10" t="n">
-        <v>10.73532228841562</v>
+        <v>1.744489871867538</v>
       </c>
       <c r="F10" t="n">
-        <v>10.29871856001947</v>
+        <v>1.673541766003165</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>22.72106055193813</v>
+        <v>3.692172339689946</v>
       </c>
       <c r="D11" t="n">
-        <v>23.6366108911473</v>
+        <v>3.840949269811436</v>
       </c>
       <c r="E11" t="n">
-        <v>10.73532228841562</v>
+        <v>1.744489871867538</v>
       </c>
       <c r="F11" t="n">
-        <v>10.29871856001947</v>
+        <v>1.673541766003165</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>27.36477205045076</v>
+        <v>4.44677545819825</v>
       </c>
       <c r="D12" t="n">
-        <v>16.80043293186605</v>
+        <v>2.730070351428234</v>
       </c>
       <c r="E12" t="n">
-        <v>10.73532228841562</v>
+        <v>1.744489871867538</v>
       </c>
       <c r="F12" t="n">
-        <v>10.29871856001947</v>
+        <v>1.673541766003165</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>32.71752282263137</v>
+        <v>5.316597458677597</v>
       </c>
       <c r="D13" t="n">
-        <v>33.72605565443033</v>
+        <v>5.480484043844929</v>
       </c>
       <c r="E13" t="n">
-        <v>10.73532228841562</v>
+        <v>1.744489871867538</v>
       </c>
       <c r="F13" t="n">
-        <v>10.29871856001947</v>
+        <v>1.673541766003165</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>37.29029376677011</v>
+        <v>6.059672737100143</v>
       </c>
       <c r="D14" t="n">
-        <v>6.250191341098406</v>
+        <v>1.015656092928491</v>
       </c>
       <c r="E14" t="n">
-        <v>10.73532228841562</v>
+        <v>1.744489871867538</v>
       </c>
       <c r="F14" t="n">
-        <v>10.29871856001947</v>
+        <v>1.673541766003165</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>37.62095145127736</v>
+        <v>6.113404610832572</v>
       </c>
       <c r="D15" t="n">
-        <v>19.1779354956821</v>
+        <v>3.116414518048341</v>
       </c>
       <c r="E15" t="n">
-        <v>10.73532228841562</v>
+        <v>1.744489871867538</v>
       </c>
       <c r="F15" t="n">
-        <v>10.29871856001947</v>
+        <v>1.673541766003165</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>22.82094808669638</v>
+        <v>3.708404064088161</v>
       </c>
       <c r="D16" t="n">
-        <v>23.70296474039016</v>
+        <v>3.851731770313401</v>
       </c>
       <c r="E16" t="n">
-        <v>10.73532228841562</v>
+        <v>1.744489871867538</v>
       </c>
       <c r="F16" t="n">
-        <v>10.29871856001947</v>
+        <v>1.673541766003165</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>36.47730184042236</v>
+        <v>5.927561549068633</v>
       </c>
       <c r="D17" t="n">
-        <v>37.50196867861511</v>
+        <v>6.094069910274955</v>
       </c>
       <c r="E17" t="n">
-        <v>10.73532228841562</v>
+        <v>1.744489871867538</v>
       </c>
       <c r="F17" t="n">
-        <v>10.29871856001947</v>
+        <v>1.673541766003165</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>7.002082974981403</v>
+        <v>1.137838483434478</v>
       </c>
       <c r="D18" t="n">
-        <v>5.792092135975618</v>
+        <v>0.9412149720960379</v>
       </c>
       <c r="E18" t="n">
-        <v>10.73532228841562</v>
+        <v>1.744489871867538</v>
       </c>
       <c r="F18" t="n">
-        <v>10.29871856001947</v>
+        <v>1.673541766003165</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>13.92481942223103</v>
+        <v>2.262783156112542</v>
       </c>
       <c r="D19" t="n">
-        <v>15.28365862127959</v>
+        <v>2.483594525957933</v>
       </c>
       <c r="E19" t="n">
-        <v>10.73532228841562</v>
+        <v>1.744489871867538</v>
       </c>
       <c r="F19" t="n">
-        <v>10.29871856001947</v>
+        <v>1.673541766003165</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
